--- a/labs/lab-06-reporting-skill/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
+++ b/labs/lab-06-reporting-skill/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
@@ -13,16 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -562,7 +556,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1332,7 +1325,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1972,7 +1965,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3260,7 +3253,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4548,7 +4541,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5188,7 +5181,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6476,7 +6469,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7091,7 +7084,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7297,7 +7289,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7479,7 +7470,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7646,7 +7636,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7690,12 +7679,10 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7706,7 +7693,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -7771,35 +7830,104 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>## OUTPUT AND REVIEW</t>
+          <t>## DASHBOARD LAYOUT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+          <t>Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+          <t>Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>## DASHBOARD STYLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>## OUTPUT AND REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
+    <row r="23">
+      <c r="A23" s="2">
         <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
